--- a/data/Mappings/MAPPINGS_RI.xlsx
+++ b/data/Mappings/MAPPINGS_RI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{7529039C-DAB5-4502-A4FA-B91C5ABC1E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5F07BE5-3E3E-45E4-954B-F4721343E0A8}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{7529039C-DAB5-4502-A4FA-B91C5ABC1E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C6C6D46-8B71-4C59-A2D8-E5FDADAD439A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">biosphere!$A$1:$M$406</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">EI_vs_RI!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">technosphere!$B$1:$I$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">technosphere!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -17156,29 +17156,26 @@
       <c r="A2" t="s">
         <v>467</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>55</v>
+      <c r="B2" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
         <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>494</v>
+        <v>223</v>
       </c>
       <c r="F2" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="G2" t="s">
         <v>174</v>
       </c>
       <c r="H2" t="s">
         <v>177</v>
-      </c>
-      <c r="I2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -17186,48 +17183,48 @@
         <v>467</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
         <v>187</v>
       </c>
       <c r="E3" t="s">
-        <v>494</v>
+        <v>232</v>
       </c>
       <c r="F3" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="G3" t="s">
         <v>174</v>
       </c>
       <c r="H3" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="I3" t="s">
-        <v>253</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>467</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>54</v>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D4" t="s">
         <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>494</v>
+        <v>225</v>
       </c>
       <c r="F4" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="G4" t="s">
         <v>174</v>
@@ -17236,56 +17233,53 @@
         <v>177</v>
       </c>
       <c r="I4" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>467</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>58</v>
+      <c r="B5" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D5" t="s">
         <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>494</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="G5" t="s">
         <v>174</v>
       </c>
       <c r="H5" t="s">
         <v>177</v>
-      </c>
-      <c r="I5" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>467</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>206</v>
+      <c r="B6" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D6" t="s">
         <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
       <c r="F6" t="s">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="G6" t="s">
         <v>174</v>
@@ -17299,7 +17293,7 @@
         <v>467</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>204</v>
@@ -17308,27 +17302,24 @@
         <v>187</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="F7" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="G7" t="s">
         <v>174</v>
       </c>
       <c r="H7" t="s">
         <v>177</v>
-      </c>
-      <c r="I7" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>467</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>27</v>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>204</v>
@@ -17337,56 +17328,50 @@
         <v>187</v>
       </c>
       <c r="E8" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="F8" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G8" t="s">
         <v>174</v>
       </c>
       <c r="H8" t="s">
         <v>177</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>467</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>50</v>
+      <c r="B9" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
         <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="F9" t="s">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="G9" t="s">
         <v>174</v>
       </c>
       <c r="H9" t="s">
         <v>177</v>
-      </c>
-      <c r="I9" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>467</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>211</v>
+      <c r="B10" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>204</v>
@@ -17395,45 +17380,45 @@
         <v>187</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="F10" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="G10" t="s">
         <v>174</v>
       </c>
       <c r="H10" t="s">
         <v>177</v>
+      </c>
+      <c r="I10" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>467</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>31</v>
+      <c r="B11" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D11" t="s">
-        <v>187</v>
+        <v>478</v>
       </c>
       <c r="E11" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" t="s">
-        <v>489</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -17441,19 +17426,19 @@
         <v>467</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D12" t="s">
         <v>187</v>
       </c>
       <c r="E12" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G12" t="s">
         <v>174</v>
@@ -17462,36 +17447,33 @@
         <v>177</v>
       </c>
       <c r="I12" t="s">
-        <v>231</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>467</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>43</v>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>187</v>
+        <v>478</v>
       </c>
       <c r="E13" t="s">
-        <v>264</v>
+        <v>183</v>
       </c>
       <c r="F13" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H13" t="s">
-        <v>177</v>
-      </c>
-      <c r="I13" t="s">
-        <v>265</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -17499,19 +17481,19 @@
         <v>467</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
         <v>187</v>
       </c>
       <c r="E14" t="s">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="F14" t="s">
-        <v>238</v>
+        <v>194</v>
       </c>
       <c r="G14" t="s">
         <v>174</v>
@@ -17520,7 +17502,7 @@
         <v>177</v>
       </c>
       <c r="I14" t="s">
-        <v>231</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -17528,54 +17510,51 @@
         <v>467</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D15" t="s">
-        <v>187</v>
+        <v>478</v>
       </c>
       <c r="E15" t="s">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="F15" t="s">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H15" t="s">
-        <v>177</v>
-      </c>
-      <c r="I15" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>467</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>37</v>
+      <c r="B16" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
+        <v>478</v>
       </c>
       <c r="E16" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="F16" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H16" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -17583,25 +17562,25 @@
         <v>467</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>187</v>
+        <v>478</v>
       </c>
       <c r="E17" t="s">
-        <v>241</v>
+        <v>183</v>
       </c>
       <c r="F17" t="s">
-        <v>242</v>
+        <v>184</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="H17" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -17609,33 +17588,36 @@
         <v>467</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D18" t="s">
         <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>247</v>
+        <v>193</v>
       </c>
       <c r="F18" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="G18" t="s">
         <v>174</v>
       </c>
       <c r="H18" t="s">
         <v>177</v>
+      </c>
+      <c r="I18" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>467</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>0</v>
+      <c r="B19" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>204</v>
@@ -17661,7 +17643,7 @@
         <v>467</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>204</v>
@@ -17670,10 +17652,10 @@
         <v>187</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="F20" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="G20" t="s">
         <v>174</v>
@@ -17687,7 +17669,7 @@
         <v>467</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>204</v>
@@ -17696,10 +17678,10 @@
         <v>187</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="F21" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="G21" t="s">
         <v>174</v>
@@ -17712,8 +17694,8 @@
       <c r="A22" t="s">
         <v>467</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>10</v>
+      <c r="B22" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>204</v>
@@ -17722,27 +17704,24 @@
         <v>187</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="F22" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="G22" t="s">
         <v>174</v>
       </c>
       <c r="H22" t="s">
         <v>177</v>
-      </c>
-      <c r="I22" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>467</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>212</v>
+      <c r="B23" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>204</v>
@@ -17751,10 +17730,10 @@
         <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="F23" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="G23" t="s">
         <v>174</v>
@@ -17768,25 +17747,25 @@
         <v>467</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>4</v>
+        <v>213</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D24" t="s">
-        <v>478</v>
+        <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="F24" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="G24" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -17794,7 +17773,7 @@
         <v>467</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>204</v>
@@ -17803,19 +17782,16 @@
         <v>187</v>
       </c>
       <c r="E25" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="F25" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="G25" t="s">
         <v>174</v>
       </c>
       <c r="H25" t="s">
-        <v>177</v>
-      </c>
-      <c r="I25" t="s">
-        <v>488</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -17823,25 +17799,25 @@
         <v>467</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>478</v>
+        <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="F26" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H26" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -17849,7 +17825,7 @@
         <v>467</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>13</v>
+        <v>465</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>204</v>
@@ -17878,25 +17854,25 @@
         <v>467</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>478</v>
+        <v>187</v>
       </c>
       <c r="E28" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G28" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H28" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -17904,7 +17880,7 @@
         <v>467</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>204</v>
@@ -17913,27 +17889,24 @@
         <v>187</v>
       </c>
       <c r="E29" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G29" t="s">
         <v>174</v>
       </c>
       <c r="H29" t="s">
         <v>177</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>467</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>34</v>
+      <c r="B30" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>204</v>
@@ -17942,19 +17915,16 @@
         <v>187</v>
       </c>
       <c r="E30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G30" t="s">
         <v>174</v>
       </c>
       <c r="H30" t="s">
         <v>177</v>
-      </c>
-      <c r="I30" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -17962,7 +17932,7 @@
         <v>467</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>204</v>
@@ -17988,7 +17958,7 @@
         <v>467</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>204</v>
@@ -18011,22 +17981,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>467</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>3</v>
+        <v>468</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D33" t="s">
         <v>187</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>494</v>
       </c>
       <c r="F33" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="G33" t="s">
         <v>174</v>
@@ -18034,13 +18004,16 @@
       <c r="H33" t="s">
         <v>177</v>
       </c>
+      <c r="I33" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>467</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>3</v>
+        <v>468</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>466</v>
@@ -18049,10 +18022,10 @@
         <v>187</v>
       </c>
       <c r="E34" t="s">
-        <v>180</v>
+        <v>494</v>
       </c>
       <c r="F34" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="G34" t="s">
         <v>174</v>
@@ -18061,15 +18034,15 @@
         <v>177</v>
       </c>
       <c r="I34" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>467</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>46</v>
+        <v>468</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>466</v>
@@ -18078,10 +18051,10 @@
         <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>262</v>
+        <v>494</v>
       </c>
       <c r="F35" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G35" t="s">
         <v>174</v>
@@ -18090,27 +18063,27 @@
         <v>177</v>
       </c>
       <c r="I35" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D36" t="s">
         <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>193</v>
+        <v>494</v>
       </c>
       <c r="F36" t="s">
-        <v>194</v>
+        <v>258</v>
       </c>
       <c r="G36" t="s">
         <v>174</v>
@@ -18119,15 +18092,15 @@
         <v>177</v>
       </c>
       <c r="I36" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>467</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>25</v>
+        <v>468</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>204</v>
@@ -18136,10 +18109,10 @@
         <v>187</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="G37" t="s">
         <v>174</v>
@@ -18150,22 +18123,22 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>467</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>49</v>
+        <v>468</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D38" t="s">
         <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="F38" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="G38" t="s">
         <v>174</v>
@@ -18174,15 +18147,15 @@
         <v>177</v>
       </c>
       <c r="I38" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>204</v>
@@ -18202,13 +18175,16 @@
       <c r="H39" t="s">
         <v>177</v>
       </c>
+      <c r="I39" s="19" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>466</v>
@@ -18217,10 +18193,10 @@
         <v>187</v>
       </c>
       <c r="E40" t="s">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="F40" t="s">
-        <v>181</v>
+        <v>260</v>
       </c>
       <c r="G40" t="s">
         <v>174</v>
@@ -18228,13 +18204,16 @@
       <c r="H40" t="s">
         <v>177</v>
       </c>
+      <c r="I40" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>467</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>45</v>
+        <v>468</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>466</v>
@@ -18243,10 +18222,10 @@
         <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G41" t="s">
         <v>174</v>
@@ -18254,13 +18233,16 @@
       <c r="H41" t="s">
         <v>177</v>
       </c>
+      <c r="I41" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>467</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>66</v>
+        <v>468</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>466</v>
@@ -18269,10 +18251,10 @@
         <v>187</v>
       </c>
       <c r="E42" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="F42" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G42" t="s">
         <v>174</v>
@@ -18281,27 +18263,27 @@
         <v>177</v>
       </c>
       <c r="I42" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D43" t="s">
         <v>187</v>
       </c>
       <c r="E43" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="F43" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="G43" t="s">
         <v>174</v>
@@ -18309,25 +18291,28 @@
       <c r="H43" t="s">
         <v>177</v>
       </c>
+      <c r="I43" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>467</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>1</v>
+        <v>468</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D44" t="s">
         <v>187</v>
       </c>
       <c r="E44" t="s">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="F44" t="s">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="G44" t="s">
         <v>174</v>
@@ -18338,10 +18323,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>467</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>15</v>
+        <v>468</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>204</v>
@@ -18350,10 +18335,10 @@
         <v>187</v>
       </c>
       <c r="E45" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F45" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G45" t="s">
         <v>174</v>
@@ -18364,22 +18349,22 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>467</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>41</v>
+        <v>468</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D46" t="s">
         <v>187</v>
       </c>
       <c r="E46" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="F46" t="s">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="G46" t="s">
         <v>174</v>
@@ -18387,13 +18372,16 @@
       <c r="H46" t="s">
         <v>177</v>
       </c>
+      <c r="I46" s="19" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>467</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>21</v>
+        <v>468</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>204</v>
@@ -18402,16 +18390,19 @@
         <v>187</v>
       </c>
       <c r="E47" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F47" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="G47" t="s">
         <v>174</v>
       </c>
       <c r="H47" t="s">
         <v>177</v>
+      </c>
+      <c r="I47" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -18419,7 +18410,7 @@
         <v>468</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>204</v>
@@ -18428,10 +18419,10 @@
         <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F48" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="G48" t="s">
         <v>174</v>
@@ -18445,33 +18436,36 @@
         <v>468</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D49" t="s">
         <v>187</v>
       </c>
       <c r="E49" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="F49" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="G49" t="s">
         <v>174</v>
       </c>
       <c r="H49" t="s">
         <v>177</v>
+      </c>
+      <c r="I49" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>468</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>63</v>
+      <c r="B50" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>466</v>
@@ -18480,27 +18474,30 @@
         <v>187</v>
       </c>
       <c r="E50" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="F50" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="G50" t="s">
         <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>177</v>
+      </c>
+      <c r="I50" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>468</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>5</v>
+      <c r="B51" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D51" t="s">
         <v>187</v>
@@ -18516,6 +18513,9 @@
       </c>
       <c r="H51" t="s">
         <v>177</v>
+      </c>
+      <c r="I51" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -18523,7 +18523,7 @@
         <v>468</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>204</v>
@@ -18532,19 +18532,16 @@
         <v>187</v>
       </c>
       <c r="E52" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F52" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G52" t="s">
         <v>174</v>
       </c>
       <c r="H52" t="s">
         <v>177</v>
-      </c>
-      <c r="I52" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -18552,28 +18549,25 @@
         <v>468</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D53" t="s">
         <v>187</v>
       </c>
       <c r="E53" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="F53" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="G53" t="s">
         <v>174</v>
       </c>
       <c r="H53" t="s">
         <v>177</v>
-      </c>
-      <c r="I53" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -18581,7 +18575,7 @@
         <v>468</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>466</v>
@@ -18607,25 +18601,28 @@
         <v>468</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>213</v>
+        <v>66</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D55" t="s">
         <v>187</v>
       </c>
       <c r="E55" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="F55" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="G55" t="s">
         <v>174</v>
       </c>
       <c r="H55" t="s">
         <v>177</v>
+      </c>
+      <c r="I55" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -18633,25 +18630,25 @@
         <v>468</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D56" t="s">
         <v>187</v>
       </c>
       <c r="E56" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="F56" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="G56" t="s">
         <v>174</v>
       </c>
       <c r="H56" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -18659,7 +18656,7 @@
         <v>468</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>204</v>
@@ -18668,16 +18665,16 @@
         <v>187</v>
       </c>
       <c r="E57" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F57" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G57" t="s">
         <v>174</v>
       </c>
       <c r="H57" t="s">
-        <v>219</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -18685,57 +18682,51 @@
         <v>468</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D58" t="s">
         <v>187</v>
       </c>
       <c r="E58" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="F58" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="G58" t="s">
         <v>174</v>
       </c>
       <c r="H58" t="s">
         <v>177</v>
-      </c>
-      <c r="I58" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>468</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>465</v>
+      <c r="B59" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D59" t="s">
         <v>187</v>
       </c>
       <c r="E59" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F59" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="G59" t="s">
         <v>174</v>
       </c>
       <c r="H59" t="s">
         <v>177</v>
-      </c>
-      <c r="I59" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -18743,7 +18734,7 @@
         <v>468</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>204</v>
@@ -18752,10 +18743,10 @@
         <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="F60" t="s">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="G60" t="s">
         <v>174</v>
@@ -18769,7 +18760,7 @@
         <v>468</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>204</v>
@@ -18788,6 +18779,9 @@
       </c>
       <c r="H61" t="s">
         <v>177</v>
+      </c>
+      <c r="I61" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -18795,19 +18789,19 @@
         <v>468</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>466</v>
+        <v>204</v>
       </c>
       <c r="D62" t="s">
         <v>187</v>
       </c>
       <c r="E62" t="s">
-        <v>493</v>
+        <v>193</v>
       </c>
       <c r="F62" t="s">
-        <v>492</v>
+        <v>194</v>
       </c>
       <c r="G62" t="s">
         <v>174</v>
@@ -18815,28 +18809,28 @@
       <c r="H62" t="s">
         <v>177</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>257</v>
+      <c r="I62" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>468</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>2</v>
+      <c r="B63" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D63" t="s">
         <v>187</v>
       </c>
       <c r="E63" t="s">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="F63" t="s">
-        <v>179</v>
+        <v>242</v>
       </c>
       <c r="G63" t="s">
         <v>174</v>
@@ -18849,34 +18843,37 @@
       <c r="A64" t="s">
         <v>468</v>
       </c>
-      <c r="B64" s="7" t="s">
-        <v>24</v>
+      <c r="B64" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D64" t="s">
-        <v>478</v>
+        <v>187</v>
       </c>
       <c r="E64" t="s">
-        <v>183</v>
+        <v>246</v>
       </c>
       <c r="F64" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="G64" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H64" t="s">
-        <v>186</v>
+        <v>177</v>
+      </c>
+      <c r="I64" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>468</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>56</v>
+      <c r="B65" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>466</v>
@@ -18885,10 +18882,10 @@
         <v>187</v>
       </c>
       <c r="E65" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F65" t="s">
-        <v>258</v>
+        <v>492</v>
       </c>
       <c r="G65" t="s">
         <v>174</v>
@@ -18896,8 +18893,8 @@
       <c r="H65" t="s">
         <v>177</v>
       </c>
-      <c r="I65" t="s">
-        <v>253</v>
+      <c r="I65" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -18905,7 +18902,7 @@
         <v>468</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>466</v>
@@ -18914,10 +18911,10 @@
         <v>187</v>
       </c>
       <c r="E66" t="s">
-        <v>247</v>
+        <v>494</v>
       </c>
       <c r="F66" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G66" t="s">
         <v>174</v>
@@ -18926,33 +18923,36 @@
         <v>177</v>
       </c>
       <c r="I66" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>468</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>32</v>
+      <c r="B67" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>204</v>
+        <v>466</v>
       </c>
       <c r="D67" t="s">
-        <v>478</v>
+        <v>187</v>
       </c>
       <c r="E67" t="s">
-        <v>183</v>
+        <v>247</v>
       </c>
       <c r="F67" t="s">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="G67" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="H67" t="s">
-        <v>186</v>
+        <v>177</v>
+      </c>
+      <c r="I67" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -19205,9 +19205,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:I76" xr:uid="{2B7552F2-809E-47BC-A2F4-BF83969FDA26}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:I76">
-      <sortCondition ref="B1:B76"/>
+  <autoFilter ref="A1:I1" xr:uid="{2B7552F2-809E-47BC-A2F4-BF83969FDA26}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I76">
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Mappings/MAPPINGS_RI.xlsx
+++ b/data/Mappings/MAPPINGS_RI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/Mappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="513" documentId="13_ncr:1_{7529039C-DAB5-4502-A4FA-B91C5ABC1E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E3D416F-9978-43D4-8B7A-FC5F02E46DCF}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="13_ncr:1_{7529039C-DAB5-4502-A4FA-B91C5ABC1E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BADACE3-EEFB-425D-917D-6EBBA5C25BA6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5591" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="584">
   <si>
     <t>Diesel</t>
   </si>
@@ -2048,6 +2048,21 @@
   </si>
   <si>
     <t>N2O</t>
+  </si>
+  <si>
+    <t>Acids</t>
+  </si>
+  <si>
+    <t>Reagants</t>
+  </si>
+  <si>
+    <t>Soda ash</t>
+  </si>
+  <si>
+    <t>soda ash, light</t>
+  </si>
+  <si>
+    <t>consumption market for soda ash, light</t>
   </si>
 </sst>
 </file>
@@ -2194,7 +2209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2228,8 +2243,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2245,6 +2259,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17219,38 +17237,38 @@
       <c r="L409" s="11"/>
       <c r="M409" s="11"/>
     </row>
-    <row r="410" spans="1:13" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A410" s="25" t="s">
-        <v>453</v>
-      </c>
-      <c r="B410" s="25" t="s">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>453</v>
+      </c>
+      <c r="B410" t="s">
         <v>384</v>
       </c>
-      <c r="C410" s="25" t="s">
+      <c r="C410" t="s">
         <v>172</v>
       </c>
-      <c r="D410" s="25" t="s">
+      <c r="D410" t="s">
         <v>172</v>
       </c>
-      <c r="E410" s="25" t="s">
+      <c r="E410" t="s">
         <v>287</v>
       </c>
-      <c r="F410" s="25" t="s">
+      <c r="F410" t="s">
         <v>385</v>
       </c>
-      <c r="G410" s="26" t="s">
+      <c r="G410" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="H410" s="25" t="s">
+      <c r="H410" t="s">
         <v>187</v>
       </c>
-      <c r="I410" s="25" t="s">
+      <c r="I410" t="s">
         <v>457</v>
       </c>
-      <c r="J410" s="25" t="s">
+      <c r="J410" t="s">
         <v>481</v>
       </c>
-      <c r="K410" s="25" t="s">
+      <c r="K410" t="s">
         <v>210</v>
       </c>
     </row>
@@ -17728,7 +17746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7552F2-809E-47BC-A2F4-BF83969FDA26}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -20498,6 +20516,84 @@
         <v>173</v>
       </c>
       <c r="H101" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>449</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D102" t="s">
+        <v>186</v>
+      </c>
+      <c r="E102" t="s">
+        <v>240</v>
+      </c>
+      <c r="F102" t="s">
+        <v>241</v>
+      </c>
+      <c r="G102" t="s">
+        <v>173</v>
+      </c>
+      <c r="H102" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>449</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D103" t="s">
+        <v>186</v>
+      </c>
+      <c r="E103" t="s">
+        <v>507</v>
+      </c>
+      <c r="F103" t="s">
+        <v>508</v>
+      </c>
+      <c r="G103" t="s">
+        <v>173</v>
+      </c>
+      <c r="H103" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>449</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D104" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E104" t="s">
+        <v>582</v>
+      </c>
+      <c r="F104" t="s">
+        <v>583</v>
+      </c>
+      <c r="G104" t="s">
+        <v>173</v>
+      </c>
+      <c r="H104" t="s">
         <v>176</v>
       </c>
     </row>
